--- a/artfynd/A 11641-2026 artfynd.xlsx
+++ b/artfynd/A 11641-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104020742</v>
+        <v>104020758</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536564.1601347233</v>
+        <v>536531</v>
       </c>
       <c r="R2" t="n">
-        <v>7026951.735897729</v>
+        <v>7026937</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104020769</v>
+        <v>104020793</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536568.2032882527</v>
+        <v>536526</v>
       </c>
       <c r="R3" t="n">
-        <v>7026951.782022459</v>
+        <v>7026914</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,11 +882,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -922,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104020743</v>
+        <v>104020769</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536567.2945733018</v>
+        <v>536568</v>
       </c>
       <c r="R4" t="n">
-        <v>7026952.669035549</v>
+        <v>7026952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1048,15 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104020710</v>
+        <v>104020810</v>
       </c>
       <c r="B5" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1088,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536567.3508734886</v>
+        <v>536533</v>
       </c>
       <c r="R5" t="n">
-        <v>7026947.734083365</v>
+        <v>7026938</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1133,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,37 +1144,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104020816</v>
+        <v>104020710</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1209,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536553.2760669194</v>
+        <v>536567</v>
       </c>
       <c r="R6" t="n">
-        <v>7026960.58554714</v>
+        <v>7026948</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,6 +1253,712 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104020743</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stenkvistkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>536567</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7026953</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104020818</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stenkvistkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>536530</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7026887</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104020816</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stenkvistkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>536553</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7026961</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104020742</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stenkvistkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>536564</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7026952</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104020797</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stenkvistkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>536627</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7027054</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104020696</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stenkvistkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>536551</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7026870</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 11641-2026 artfynd.xlsx
+++ b/artfynd/A 11641-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020793</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020769</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020810</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020710</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020743</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1499,6 +1534,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020818</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1615,6 +1655,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020816</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1731,6 +1776,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020742</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1847,6 +1897,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020797</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1963,8 +2018,26 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020696</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>